--- a/04-pinecastle-software-grc-program/02-nist-csf-gap-assessment/artifacts/Pinecastle-NIST-CSF-2.0-Gap-Assessment.xlsx
+++ b/04-pinecastle-software-grc-program/02-nist-csf-gap-assessment/artifacts/Pinecastle-NIST-CSF-2.0-Gap-Assessment.xlsx
@@ -717,9 +717,9 @@
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
